--- a/publish/20260830.xlsx
+++ b/publish/20260830.xlsx
@@ -2349,11 +2349,6 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:AF4"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Z2" r:id="rId3"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
